--- a/詩經/xlsx/詞彙.xlsx
+++ b/詩經/xlsx/詞彙.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\ShijingNature\詩經\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D17F18B-6AA2-4CC0-BF2C-7907519633E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246548DD-FC84-4507-9592-48A6BAFC76C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="610">
   <si>
     <t>水體</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2121,10 +2121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>微生物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>雪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2448,14 +2444,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>魚類</t>
   </si>
   <si>
     <t>魚類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兩棲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3064,7 +3060,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
@@ -3356,7 +3352,7 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D47" t="s">
         <v>71</v>
@@ -3439,7 +3435,7 @@
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D54" t="s">
         <v>95</v>
@@ -3456,7 +3452,7 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D55" t="s">
         <v>95</v>
@@ -4507,7 +4503,7 @@
         <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D150" t="s">
         <v>226</v>
@@ -4810,7 +4806,7 @@
         <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D177" t="s">
         <v>265</v>
@@ -4838,7 +4834,7 @@
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D179" t="s">
         <v>265</v>
@@ -4855,7 +4851,7 @@
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D180" t="s">
         <v>265</v>
@@ -4927,7 +4923,7 @@
         <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D186" t="s">
         <v>265</v>
@@ -4944,7 +4940,7 @@
         <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D187" t="s">
         <v>265</v>
@@ -5731,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D258" t="s">
         <v>386</v>
@@ -5748,7 +5744,7 @@
         <v>7</v>
       </c>
       <c r="C259" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D259" t="s">
         <v>386</v>
@@ -5930,7 +5926,7 @@
         <v>7</v>
       </c>
       <c r="C275" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D275" t="s">
         <v>408</v>
@@ -5947,7 +5943,7 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D276" t="s">
         <v>408</v>
@@ -5964,7 +5960,7 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D277" t="s">
         <v>408</v>
@@ -5981,7 +5977,7 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D278" t="s">
         <v>408</v>
@@ -6196,7 +6192,7 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D297" t="s">
         <v>432</v>
@@ -6763,7 +6759,7 @@
         <v>7</v>
       </c>
       <c r="C348" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D348" t="s">
         <v>502</v>
@@ -6945,51 +6941,51 @@
         <v>7</v>
       </c>
       <c r="C364" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D364" t="s">
         <v>525</v>
       </c>
       <c r="E364" t="s">
-        <v>526</v>
+        <v>40</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B365" t="s">
         <v>315</v>
       </c>
       <c r="C365" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>529</v>
+      </c>
+      <c r="B366" t="s">
+        <v>7</v>
+      </c>
+      <c r="C366" t="s">
         <v>530</v>
-      </c>
-      <c r="B366" t="s">
-        <v>7</v>
-      </c>
-      <c r="C366" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B367" t="s">
         <v>315</v>
       </c>
       <c r="C367" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B368" t="s">
         <v>7</v>
@@ -7000,7 +6996,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B369" t="s">
         <v>2</v>
@@ -7011,7 +7007,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B370" t="s">
         <v>2</v>
@@ -7022,95 +7018,95 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B371" t="s">
         <v>315</v>
       </c>
       <c r="C371" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B372" t="s">
         <v>124</v>
       </c>
       <c r="C372" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B373" t="s">
         <v>124</v>
       </c>
       <c r="C373" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B374" t="s">
         <v>124</v>
       </c>
       <c r="C374" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B375" t="s">
         <v>124</v>
       </c>
       <c r="C375" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B376" t="s">
         <v>124</v>
       </c>
       <c r="C376" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B377" t="s">
         <v>124</v>
       </c>
       <c r="C377" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B378" t="s">
         <v>124</v>
       </c>
       <c r="C378" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B379" t="s">
         <v>7</v>
@@ -7121,29 +7117,29 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>548</v>
+      </c>
+      <c r="B380" t="s">
+        <v>2</v>
+      </c>
+      <c r="C380" t="s">
         <v>549</v>
-      </c>
-      <c r="B380" t="s">
-        <v>2</v>
-      </c>
-      <c r="C380" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B381" t="s">
         <v>124</v>
       </c>
       <c r="C381" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B382" t="s">
         <v>7</v>
@@ -7154,51 +7150,51 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B383" t="s">
         <v>124</v>
       </c>
       <c r="C383" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B384" t="s">
         <v>124</v>
       </c>
       <c r="C384" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B385" t="s">
         <v>124</v>
       </c>
       <c r="C385" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B386" t="s">
         <v>124</v>
       </c>
       <c r="C386" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B387" t="s">
         <v>2</v>
@@ -7209,35 +7205,35 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>557</v>
+      </c>
+      <c r="B388" t="s">
+        <v>7</v>
+      </c>
+      <c r="C388" t="s">
+        <v>606</v>
+      </c>
+      <c r="D388" t="s">
+        <v>538</v>
+      </c>
+      <c r="E388" t="s">
         <v>558</v>
-      </c>
-      <c r="B388" t="s">
-        <v>7</v>
-      </c>
-      <c r="C388" t="s">
-        <v>607</v>
-      </c>
-      <c r="D388" t="s">
-        <v>539</v>
-      </c>
-      <c r="E388" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B389" t="s">
         <v>5</v>
       </c>
       <c r="C389" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B390" t="s">
         <v>5</v>
@@ -7248,7 +7244,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B391" t="s">
         <v>5</v>
@@ -7259,7 +7255,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B392" t="s">
         <v>7</v>
@@ -7270,18 +7266,18 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B393" t="s">
         <v>5</v>
       </c>
       <c r="C393" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B394" t="s">
         <v>7</v>
@@ -7292,41 +7288,41 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B395" t="s">
         <v>7</v>
       </c>
       <c r="C395" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D395" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E395" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B396" t="s">
         <v>7</v>
       </c>
       <c r="C396" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D396" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E396" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B397" t="s">
         <v>2</v>
@@ -7337,7 +7333,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B398" t="s">
         <v>2</v>
@@ -7348,7 +7344,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B399" t="s">
         <v>2</v>
@@ -7359,7 +7355,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B400" t="s">
         <v>2</v>
@@ -7370,7 +7366,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B401" t="s">
         <v>2</v>
@@ -7381,7 +7377,7 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B402" t="s">
         <v>2</v>
@@ -7392,7 +7388,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B403" t="s">
         <v>2</v>
@@ -7403,7 +7399,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B404" t="s">
         <v>2</v>
@@ -7414,7 +7410,7 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B405" t="s">
         <v>2</v>
@@ -7425,7 +7421,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B406" t="s">
         <v>5</v>
@@ -7436,7 +7432,7 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B407" t="s">
         <v>2</v>
@@ -7447,7 +7443,7 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B408" t="s">
         <v>2</v>
@@ -7458,7 +7454,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B409" t="s">
         <v>124</v>
@@ -7469,7 +7465,7 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B410" t="s">
         <v>2</v>
@@ -7480,7 +7476,7 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B411" t="s">
         <v>2</v>
@@ -7491,7 +7487,7 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B412" t="s">
         <v>7</v>
@@ -7502,7 +7498,7 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B413" t="s">
         <v>2</v>
@@ -7513,7 +7509,7 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B414" t="s">
         <v>7</v>
@@ -7524,7 +7520,7 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B415" t="s">
         <v>7</v>
@@ -7535,7 +7531,7 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B416" t="s">
         <v>2</v>
@@ -7546,7 +7542,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B417" t="s">
         <v>2</v>
@@ -7557,24 +7553,24 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>590</v>
+      </c>
+      <c r="B418" t="s">
+        <v>7</v>
+      </c>
+      <c r="C418" t="s">
+        <v>606</v>
+      </c>
+      <c r="D418" t="s">
         <v>591</v>
       </c>
-      <c r="B418" t="s">
-        <v>7</v>
-      </c>
-      <c r="C418" t="s">
-        <v>607</v>
-      </c>
-      <c r="D418" t="s">
-        <v>592</v>
-      </c>
       <c r="E418" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B419" t="s">
         <v>2</v>
@@ -7585,69 +7581,69 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B420" t="s">
         <v>7</v>
       </c>
       <c r="C420" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D420" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E420" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B421" t="s">
         <v>7</v>
       </c>
       <c r="C421" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D421" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E421" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B422" t="s">
         <v>7</v>
       </c>
       <c r="C422" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D422" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E422" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B423" t="s">
         <v>7</v>
       </c>
       <c r="C423" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B424" t="s">
         <v>4</v>
@@ -7658,7 +7654,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B425" t="s">
         <v>2</v>
@@ -7669,7 +7665,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B426" t="s">
         <v>7</v>
@@ -7680,7 +7676,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B427" t="s">
         <v>7</v>
@@ -7691,35 +7687,35 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B428" t="s">
         <v>5</v>
       </c>
       <c r="C428" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>603</v>
+      </c>
+      <c r="B429" t="s">
+        <v>7</v>
+      </c>
+      <c r="C429" t="s">
+        <v>607</v>
+      </c>
+      <c r="D429" t="s">
+        <v>601</v>
+      </c>
+      <c r="E429" t="s">
         <v>604</v>
-      </c>
-      <c r="B429" t="s">
-        <v>7</v>
-      </c>
-      <c r="C429" t="s">
-        <v>609</v>
-      </c>
-      <c r="D429" t="s">
-        <v>602</v>
-      </c>
-      <c r="E429" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B430" t="s">
         <v>7</v>
@@ -7933,22 +7929,22 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>

--- a/詩經/xlsx/詞彙.xlsx
+++ b/詩經/xlsx/詞彙.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\ShijingNature\詩經\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246548DD-FC84-4507-9592-48A6BAFC76C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365924F6-B79B-4F06-B360-BFF9EF614727}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="618">
   <si>
     <t>水體</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1039,9 +1039,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交通</t>
-  </si>
-  <si>
     <t>跋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1178,10 +1175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>松</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1921,10 +1914,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>互動</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>湄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2452,6 +2441,49 @@
   </si>
   <si>
     <t>兩棲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地景環境</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原野</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>涉水</t>
+  </si>
+  <si>
+    <t>涉水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>涉水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改歲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卒歲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其蚤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2799,7 +2831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E430"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2831,7 +2863,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -3060,7 +3092,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
@@ -3202,7 +3234,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>255</v>
+        <v>611</v>
       </c>
       <c r="D35" t="s">
         <v>58</v>
@@ -3352,7 +3384,7 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D47" t="s">
         <v>71</v>
@@ -3435,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D54" t="s">
         <v>95</v>
@@ -3452,7 +3484,7 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D55" t="s">
         <v>95</v>
@@ -4096,7 +4128,7 @@
         <v>5</v>
       </c>
       <c r="C113" t="s">
-        <v>255</v>
+        <v>611</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -4200,7 +4232,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B123" t="s">
         <v>5</v>
@@ -4228,18 +4260,18 @@
         <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>255</v>
+        <v>610</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B126" t="s">
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>255</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -4250,7 +4282,7 @@
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>255</v>
+        <v>610</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,7 +4419,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B140" t="s">
         <v>11</v>
@@ -4503,7 +4535,7 @@
         <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D150" t="s">
         <v>226</v>
@@ -4520,7 +4552,7 @@
         <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>255</v>
+        <v>610</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -4531,7 +4563,7 @@
         <v>5</v>
       </c>
       <c r="C152" t="s">
-        <v>255</v>
+        <v>610</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -4734,13 +4766,13 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B171" t="s">
         <v>5</v>
       </c>
       <c r="C171" t="s">
-        <v>255</v>
+        <v>612</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4751,73 +4783,73 @@
         <v>5</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B173" t="s">
         <v>4</v>
       </c>
       <c r="C173" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>258</v>
+      </c>
+      <c r="B174" t="s">
+        <v>2</v>
+      </c>
+      <c r="C174" t="s">
         <v>259</v>
-      </c>
-      <c r="B174" t="s">
-        <v>2</v>
-      </c>
-      <c r="C174" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B175" t="s">
         <v>4</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B176" t="s">
         <v>4</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>263</v>
+      </c>
+      <c r="B177" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" t="s">
+        <v>603</v>
+      </c>
+      <c r="D177" t="s">
         <v>264</v>
       </c>
-      <c r="B177" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" t="s">
-        <v>606</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>265</v>
-      </c>
-      <c r="E177" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B178" t="s">
         <v>2</v>
@@ -4828,41 +4860,41 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D179" t="s">
+        <v>264</v>
+      </c>
+      <c r="E179" t="s">
         <v>265</v>
-      </c>
-      <c r="E179" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D180" t="s">
+        <v>264</v>
+      </c>
+      <c r="E180" t="s">
         <v>265</v>
-      </c>
-      <c r="E180" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B181" t="s">
         <v>5</v>
@@ -4873,18 +4905,18 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B182" t="s">
         <v>4</v>
       </c>
       <c r="C182" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
@@ -4895,7 +4927,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
@@ -4906,52 +4938,52 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B185" t="s">
         <v>5</v>
       </c>
       <c r="C185" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B186" t="s">
         <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D186" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E186" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>277</v>
+      </c>
+      <c r="B187" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" t="s">
+        <v>604</v>
+      </c>
+      <c r="D187" t="s">
+        <v>264</v>
+      </c>
+      <c r="E187" t="s">
         <v>278</v>
-      </c>
-      <c r="B187" t="s">
-        <v>7</v>
-      </c>
-      <c r="C187" t="s">
-        <v>607</v>
-      </c>
-      <c r="D187" t="s">
-        <v>265</v>
-      </c>
-      <c r="E187" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B188" t="s">
         <v>2</v>
@@ -4962,51 +4994,51 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B189" t="s">
         <v>124</v>
       </c>
       <c r="C189" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>282</v>
+      </c>
+      <c r="B190" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" t="s">
         <v>283</v>
-      </c>
-      <c r="B190" t="s">
-        <v>2</v>
-      </c>
-      <c r="C190" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B191" t="s">
         <v>124</v>
       </c>
       <c r="C191" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B192" t="s">
         <v>4</v>
       </c>
       <c r="C192" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B193" t="s">
         <v>2</v>
@@ -5017,18 +5049,18 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B194" t="s">
         <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>290</v>
+        <v>613</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B195" t="s">
         <v>2</v>
@@ -5039,7 +5071,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B196" t="s">
         <v>2</v>
@@ -5050,7 +5082,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B197" t="s">
         <v>2</v>
@@ -5061,29 +5093,29 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B198" t="s">
         <v>5</v>
       </c>
       <c r="C198" t="s">
-        <v>290</v>
+        <v>613</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B199" t="s">
         <v>5</v>
       </c>
       <c r="C199" t="s">
-        <v>290</v>
+        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B200" t="s">
         <v>2</v>
@@ -5094,62 +5126,62 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B201" t="s">
         <v>4</v>
       </c>
       <c r="C201" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B202" t="s">
         <v>4</v>
       </c>
       <c r="C202" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B203" t="s">
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>304</v>
+      </c>
+      <c r="B204" t="s">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
         <v>306</v>
-      </c>
-      <c r="B204" t="s">
-        <v>2</v>
-      </c>
-      <c r="C204" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B205" t="s">
         <v>2</v>
       </c>
       <c r="C205" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B206" t="s">
         <v>2</v>
@@ -5160,7 +5192,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B207" t="s">
         <v>2</v>
@@ -5171,7 +5203,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B208" t="s">
         <v>2</v>
@@ -5182,7 +5214,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B209" t="s">
         <v>2</v>
@@ -5193,7 +5225,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B210" t="s">
         <v>2</v>
@@ -5204,18 +5236,18 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>312</v>
+      </c>
+      <c r="B211" t="s">
+        <v>313</v>
+      </c>
+      <c r="C211" t="s">
         <v>314</v>
-      </c>
-      <c r="B211" t="s">
-        <v>315</v>
-      </c>
-      <c r="C211" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B212" t="s">
         <v>7</v>
@@ -5226,7 +5258,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B213" t="s">
         <v>7</v>
@@ -5237,7 +5269,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B214" t="s">
         <v>7</v>
@@ -5248,51 +5280,51 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B215" t="s">
         <v>5</v>
       </c>
       <c r="C215" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B216" t="s">
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B217" t="s">
         <v>2</v>
       </c>
       <c r="C217" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B218" t="s">
         <v>11</v>
       </c>
       <c r="C218" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B219" t="s">
         <v>2</v>
@@ -5303,51 +5335,51 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B220" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C220" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B221" t="s">
         <v>5</v>
       </c>
       <c r="C221" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B222" t="s">
         <v>5</v>
       </c>
       <c r="C222" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B223" t="s">
         <v>5</v>
       </c>
       <c r="C223" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B224" t="s">
         <v>2</v>
@@ -5358,7 +5390,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B225" t="s">
         <v>4</v>
@@ -5369,7 +5401,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B226" t="s">
         <v>4</v>
@@ -5380,7 +5412,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B227" t="s">
         <v>4</v>
@@ -5391,7 +5423,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B228" t="s">
         <v>2</v>
@@ -5402,7 +5434,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B229" t="s">
         <v>2</v>
@@ -5413,73 +5445,73 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B230" t="s">
         <v>4</v>
       </c>
       <c r="C230" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B231" t="s">
         <v>2</v>
       </c>
       <c r="C231" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B232" t="s">
         <v>2</v>
       </c>
       <c r="C232" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B233" t="s">
         <v>2</v>
       </c>
       <c r="C233" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B234" t="s">
         <v>5</v>
       </c>
       <c r="C234" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B235" t="s">
         <v>5</v>
       </c>
       <c r="C235" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
@@ -5490,18 +5522,18 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>355</v>
+        <v>607</v>
       </c>
       <c r="B237" t="s">
-        <v>7</v>
+        <v>608</v>
       </c>
       <c r="C237" t="s">
-        <v>30</v>
+        <v>609</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
@@ -5512,7 +5544,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
@@ -5523,73 +5555,73 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B240" t="s">
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>359</v>
+        <v>30</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B241" t="s">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>30</v>
+        <v>357</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>373</v>
+        <v>30</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B244" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C244" t="s">
-        <v>42</v>
+        <v>361</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B245" t="s">
         <v>2</v>
       </c>
       <c r="C245" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B246" t="s">
         <v>2</v>
@@ -5600,117 +5632,117 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B247" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C247" t="s">
-        <v>368</v>
+        <v>24</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B248" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C248" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B249" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C249" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B250" t="s">
         <v>11</v>
       </c>
       <c r="C250" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B251" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C251" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B252" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C252" t="s">
-        <v>19</v>
+        <v>374</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B253" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C253" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B254" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="C254" t="s">
-        <v>381</v>
+        <v>246</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B255" t="s">
-        <v>2</v>
+        <v>378</v>
       </c>
       <c r="C255" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="B256" t="s">
         <v>2</v>
       </c>
       <c r="C256" t="s">
-        <v>42</v>
+        <v>381</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>384</v>
+        <v>518</v>
       </c>
       <c r="B257" t="s">
         <v>2</v>
@@ -5721,74 +5753,74 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B258" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C258" t="s">
-        <v>606</v>
-      </c>
-      <c r="D258" t="s">
-        <v>386</v>
-      </c>
-      <c r="E258" t="s">
-        <v>387</v>
+        <v>42</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B259" t="s">
         <v>7</v>
       </c>
       <c r="C259" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D259" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E259" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B260" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="C260" t="s">
-        <v>390</v>
+        <v>603</v>
+      </c>
+      <c r="D260" t="s">
+        <v>384</v>
+      </c>
+      <c r="E260" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B261" t="s">
         <v>124</v>
       </c>
       <c r="C261" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B262" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C262" t="s">
-        <v>30</v>
+        <v>388</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B263" t="s">
         <v>7</v>
@@ -5799,306 +5831,306 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B264" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="C264" t="s">
-        <v>390</v>
+        <v>30</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B265" t="s">
         <v>124</v>
       </c>
       <c r="C265" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B266" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C266" t="s">
-        <v>24</v>
+        <v>388</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C267" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B268" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="C268" t="s">
-        <v>390</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B269" t="s">
         <v>124</v>
       </c>
       <c r="C269" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B270" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C270" t="s">
-        <v>19</v>
+        <v>388</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C271" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B272" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C272" t="s">
-        <v>19</v>
+        <v>247</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B273" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C273" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B274" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C274" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C275" t="s">
-        <v>607</v>
-      </c>
-      <c r="D275" t="s">
-        <v>408</v>
-      </c>
-      <c r="E275" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>402</v>
+      </c>
+      <c r="B276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C276" t="s">
+        <v>604</v>
+      </c>
+      <c r="D276" t="s">
+        <v>406</v>
+      </c>
+      <c r="E276" t="s">
         <v>405</v>
-      </c>
-      <c r="B276" t="s">
-        <v>7</v>
-      </c>
-      <c r="C276" t="s">
-        <v>607</v>
-      </c>
-      <c r="D276" t="s">
-        <v>408</v>
-      </c>
-      <c r="E276" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>403</v>
+      </c>
+      <c r="B277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277" t="s">
+        <v>604</v>
+      </c>
+      <c r="D277" t="s">
         <v>406</v>
       </c>
-      <c r="B277" t="s">
-        <v>7</v>
-      </c>
-      <c r="C277" t="s">
-        <v>607</v>
-      </c>
-      <c r="D277" t="s">
-        <v>408</v>
-      </c>
       <c r="E277" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B278" t="s">
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D278" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E278" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B279" t="s">
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>30</v>
+        <v>604</v>
+      </c>
+      <c r="D279" t="s">
+        <v>406</v>
+      </c>
+      <c r="E279" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B280" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>411</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B281" t="s">
         <v>11</v>
       </c>
       <c r="C281" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B282" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C282" t="s">
-        <v>156</v>
+        <v>409</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B283" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C283" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B284" t="s">
         <v>2</v>
       </c>
       <c r="C284" t="s">
-        <v>416</v>
+        <v>19</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B285" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C285" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B286" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C286" t="s">
-        <v>46</v>
+        <v>416</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B287" t="s">
         <v>2</v>
       </c>
       <c r="C287" t="s">
-        <v>421</v>
+        <v>46</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B288" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C288" t="s">
-        <v>246</v>
+        <v>419</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B289" t="s">
         <v>4</v>
@@ -6109,7 +6141,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B290" t="s">
         <v>4</v>
@@ -6120,18 +6152,18 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B291" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C291" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B292" t="s">
         <v>5</v>
@@ -6142,7 +6174,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B293" t="s">
         <v>5</v>
@@ -6153,29 +6185,29 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B294" t="s">
         <v>5</v>
       </c>
       <c r="C294" t="s">
-        <v>429</v>
+        <v>247</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B295" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C295" t="s">
-        <v>30</v>
+        <v>427</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B296" t="s">
         <v>7</v>
@@ -6186,189 +6218,189 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B297" t="s">
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>606</v>
-      </c>
-      <c r="D297" t="s">
-        <v>432</v>
-      </c>
-      <c r="E297" t="s">
-        <v>433</v>
+        <v>30</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B298" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="C298" t="s">
-        <v>434</v>
+        <v>603</v>
+      </c>
+      <c r="D298" t="s">
+        <v>430</v>
+      </c>
+      <c r="E298" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B299" t="s">
         <v>124</v>
       </c>
       <c r="C299" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B300" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C300" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B301" t="s">
         <v>2</v>
       </c>
       <c r="C301" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B302" t="s">
         <v>2</v>
       </c>
       <c r="C302" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B303" t="s">
         <v>2</v>
       </c>
       <c r="C303" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B304" t="s">
         <v>2</v>
       </c>
       <c r="C304" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B305" t="s">
         <v>2</v>
       </c>
       <c r="C305" t="s">
-        <v>46</v>
+        <v>419</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B306" t="s">
         <v>2</v>
       </c>
       <c r="C306" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B307" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C307" t="s">
-        <v>434</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B308" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C308" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B309" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C309" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B310" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C310" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B311" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C311" t="s">
-        <v>247</v>
+        <v>419</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B312" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C312" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B313" t="s">
         <v>2</v>
@@ -6379,62 +6411,62 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B314" t="s">
         <v>2</v>
       </c>
       <c r="C314" t="s">
-        <v>19</v>
+        <v>233</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B315" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C315" t="s">
-        <v>454</v>
+        <v>19</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B316" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C316" t="s">
-        <v>246</v>
+        <v>452</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B317" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C317" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B318" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C318" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B319" t="s">
         <v>7</v>
@@ -6445,7 +6477,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B320" t="s">
         <v>7</v>
@@ -6456,7 +6488,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B321" t="s">
         <v>7</v>
@@ -6467,7 +6499,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B322" t="s">
         <v>7</v>
@@ -6478,7 +6510,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B323" t="s">
         <v>7</v>
@@ -6489,7 +6521,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B324" t="s">
         <v>7</v>
@@ -6500,73 +6532,73 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B325" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C325" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B326" t="s">
-        <v>315</v>
+        <v>2</v>
       </c>
       <c r="C326" t="s">
-        <v>469</v>
+        <v>19</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B327" t="s">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="C327" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B328" t="s">
         <v>5</v>
       </c>
       <c r="C328" t="s">
-        <v>476</v>
+        <v>610</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B329" t="s">
         <v>5</v>
       </c>
       <c r="C329" t="s">
-        <v>476</v>
+        <v>610</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B330" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C330" t="s">
-        <v>74</v>
+        <v>610</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B331" t="s">
         <v>4</v>
@@ -6577,51 +6609,51 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B332" t="s">
         <v>4</v>
       </c>
       <c r="C332" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B333" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C333" t="s">
-        <v>421</v>
+        <v>246</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B334" t="s">
         <v>2</v>
       </c>
       <c r="C334" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B335" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C335" t="s">
-        <v>3</v>
+        <v>419</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B336" t="s">
         <v>7</v>
@@ -6632,156 +6664,156 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B337" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C337" t="s">
-        <v>421</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B338" t="s">
         <v>2</v>
       </c>
       <c r="C338" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B339" t="s">
         <v>2</v>
       </c>
       <c r="C339" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B340" t="s">
         <v>2</v>
       </c>
       <c r="C340" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B341" t="s">
         <v>2</v>
       </c>
       <c r="C341" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B342" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C342" t="s">
-        <v>246</v>
+        <v>419</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B343" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C343" t="s">
-        <v>9</v>
+        <v>246</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B344" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C344" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B345" t="s">
         <v>2</v>
       </c>
       <c r="C345" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B346" t="s">
         <v>2</v>
       </c>
       <c r="C346" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B347" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C347" t="s">
-        <v>500</v>
+        <v>46</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B348" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C348" t="s">
-        <v>607</v>
-      </c>
-      <c r="D348" t="s">
-        <v>502</v>
-      </c>
-      <c r="E348" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B349" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C349" t="s">
-        <v>19</v>
+        <v>604</v>
+      </c>
+      <c r="D349" t="s">
+        <v>499</v>
+      </c>
+      <c r="E349" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B350" t="s">
         <v>2</v>
@@ -6792,128 +6824,128 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B351" t="s">
         <v>2</v>
       </c>
       <c r="C351" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B352" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C352" t="s">
-        <v>508</v>
+        <v>24</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B353" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C353" t="s">
-        <v>3</v>
+        <v>505</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B354" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C354" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B355" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C355" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B356" t="s">
         <v>2</v>
       </c>
       <c r="C356" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B357" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C357" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B358" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C358" t="s">
-        <v>500</v>
+        <v>74</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B359" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C359" t="s">
-        <v>74</v>
+        <v>497</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B360" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C360" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B361" t="s">
         <v>2</v>
       </c>
       <c r="C361" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B362" t="s">
         <v>2</v>
@@ -6924,90 +6956,90 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B363" t="s">
         <v>2</v>
       </c>
       <c r="C363" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B364" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C364" t="s">
-        <v>606</v>
-      </c>
-      <c r="D364" t="s">
-        <v>525</v>
-      </c>
-      <c r="E364" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B365" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="C365" t="s">
-        <v>528</v>
+        <v>603</v>
+      </c>
+      <c r="D365" t="s">
+        <v>522</v>
+      </c>
+      <c r="E365" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B366" t="s">
-        <v>7</v>
+        <v>313</v>
       </c>
       <c r="C366" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B367" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="C367" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B368" t="s">
-        <v>7</v>
+        <v>313</v>
       </c>
       <c r="C368" t="s">
-        <v>3</v>
+        <v>525</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B369" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C369" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B370" t="s">
         <v>2</v>
@@ -7018,120 +7050,120 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B371" t="s">
-        <v>315</v>
+        <v>2</v>
       </c>
       <c r="C371" t="s">
-        <v>537</v>
+        <v>19</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B372" t="s">
-        <v>124</v>
+        <v>313</v>
       </c>
       <c r="C372" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B373" t="s">
         <v>124</v>
       </c>
       <c r="C373" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B374" t="s">
         <v>124</v>
       </c>
       <c r="C374" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B375" t="s">
         <v>124</v>
       </c>
       <c r="C375" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B376" t="s">
         <v>124</v>
       </c>
       <c r="C376" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B377" t="s">
         <v>124</v>
       </c>
       <c r="C377" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B378" t="s">
         <v>124</v>
       </c>
       <c r="C378" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B379" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C379" t="s">
-        <v>3</v>
+        <v>543</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B380" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>549</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B381" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C381" t="s">
         <v>546</v>
@@ -7139,112 +7171,112 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B382" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C382" t="s">
-        <v>3</v>
+        <v>543</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B383" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="C383" t="s">
-        <v>546</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B384" t="s">
         <v>124</v>
       </c>
       <c r="C384" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B385" t="s">
         <v>124</v>
       </c>
       <c r="C385" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B386" t="s">
         <v>124</v>
       </c>
       <c r="C386" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B387" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C387" t="s">
-        <v>19</v>
+        <v>543</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B388" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C388" t="s">
-        <v>606</v>
-      </c>
-      <c r="D388" t="s">
-        <v>538</v>
-      </c>
-      <c r="E388" t="s">
-        <v>558</v>
+        <v>19</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B389" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C389" t="s">
-        <v>563</v>
+        <v>603</v>
+      </c>
+      <c r="D389" t="s">
+        <v>535</v>
+      </c>
+      <c r="E389" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B390" t="s">
         <v>5</v>
       </c>
       <c r="C390" t="s">
-        <v>247</v>
+        <v>560</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B391" t="s">
         <v>5</v>
@@ -7255,85 +7287,85 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B392" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C392" t="s">
-        <v>30</v>
+        <v>247</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B393" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C393" t="s">
-        <v>563</v>
+        <v>30</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B394" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C394" t="s">
-        <v>30</v>
+        <v>560</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B395" t="s">
         <v>7</v>
       </c>
       <c r="C395" t="s">
-        <v>606</v>
-      </c>
-      <c r="D395" t="s">
-        <v>538</v>
-      </c>
-      <c r="E395" t="s">
-        <v>558</v>
+        <v>30</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B396" t="s">
         <v>7</v>
       </c>
       <c r="C396" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D396" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E396" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B397" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C397" t="s">
-        <v>46</v>
+        <v>603</v>
+      </c>
+      <c r="D397" t="s">
+        <v>535</v>
+      </c>
+      <c r="E397" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B398" t="s">
         <v>2</v>
@@ -7344,7 +7376,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B399" t="s">
         <v>2</v>
@@ -7355,29 +7387,29 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B400" t="s">
         <v>2</v>
       </c>
       <c r="C400" t="s">
-        <v>233</v>
+        <v>46</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B401" t="s">
         <v>2</v>
       </c>
       <c r="C401" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B402" t="s">
         <v>2</v>
@@ -7388,7 +7420,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B403" t="s">
         <v>2</v>
@@ -7399,51 +7431,51 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B404" t="s">
         <v>2</v>
       </c>
       <c r="C404" t="s">
-        <v>233</v>
+        <v>46</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B405" t="s">
         <v>2</v>
       </c>
       <c r="C405" t="s">
-        <v>24</v>
+        <v>233</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B406" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C406" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B407" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C407" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B408" t="s">
         <v>2</v>
@@ -7454,229 +7486,229 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B409" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C409" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B410" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="C410" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B411" t="s">
         <v>2</v>
       </c>
       <c r="C411" t="s">
-        <v>233</v>
+        <v>19</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B412" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C412" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B413" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C413" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B414" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C414" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B415" t="s">
         <v>7</v>
       </c>
       <c r="C415" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B416" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C416" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B417" t="s">
         <v>2</v>
       </c>
       <c r="C417" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B418" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C418" t="s">
-        <v>606</v>
-      </c>
-      <c r="D418" t="s">
-        <v>591</v>
-      </c>
-      <c r="E418" t="s">
-        <v>558</v>
+        <v>19</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B419" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C419" t="s">
-        <v>46</v>
+        <v>603</v>
+      </c>
+      <c r="D419" t="s">
+        <v>588</v>
+      </c>
+      <c r="E419" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B420" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C420" t="s">
-        <v>606</v>
-      </c>
-      <c r="D420" t="s">
-        <v>591</v>
-      </c>
-      <c r="E420" t="s">
-        <v>558</v>
+        <v>46</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B421" t="s">
         <v>7</v>
       </c>
       <c r="C421" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D421" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E421" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B422" t="s">
         <v>7</v>
       </c>
       <c r="C422" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D422" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E422" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B423" t="s">
         <v>7</v>
       </c>
       <c r="C423" t="s">
-        <v>530</v>
+        <v>603</v>
+      </c>
+      <c r="D423" t="s">
+        <v>588</v>
+      </c>
+      <c r="E423" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B424" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C424" t="s">
-        <v>246</v>
+        <v>527</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B425" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C425" t="s">
-        <v>46</v>
+        <v>246</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B426" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C426" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B427" t="s">
         <v>7</v>
@@ -7687,46 +7719,101 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B428" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C428" t="s">
-        <v>563</v>
+        <v>30</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B429" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C429" t="s">
-        <v>607</v>
-      </c>
-      <c r="D429" t="s">
-        <v>601</v>
-      </c>
-      <c r="E429" t="s">
-        <v>604</v>
+        <v>560</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B430" t="s">
         <v>7</v>
       </c>
       <c r="C430" t="s">
+        <v>604</v>
+      </c>
+      <c r="D430" t="s">
+        <v>598</v>
+      </c>
+      <c r="E430" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>602</v>
+      </c>
+      <c r="B431" t="s">
+        <v>7</v>
+      </c>
+      <c r="C431" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>614</v>
+      </c>
+      <c r="B432" t="s">
+        <v>124</v>
+      </c>
+      <c r="C432" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>615</v>
+      </c>
+      <c r="B433" t="s">
+        <v>124</v>
+      </c>
+      <c r="C433" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>617</v>
+      </c>
+      <c r="B434" t="s">
+        <v>124</v>
+      </c>
+      <c r="C434" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>616</v>
+      </c>
+      <c r="B435" t="s">
+        <v>124</v>
+      </c>
+      <c r="C435" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A139 A141:A310 A312:A1048576">
+  <conditionalFormatting sqref="A313:A1048576 A1:A139 A141:A311">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A140">
@@ -7814,137 +7901,137 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
